--- a/extenbooks/S801_extenbook.xlsx
+++ b/extenbooks/S801_extenbook.xlsx
@@ -657,10 +657,10 @@
         <v>1965</v>
       </c>
       <c r="B4" t="n">
+        <v>103.06</v>
+      </c>
+      <c r="C4" t="n">
         <v>102.67</v>
-      </c>
-      <c r="C4" t="n">
-        <v>103.06</v>
       </c>
     </row>
     <row r="5">
@@ -668,10 +668,10 @@
         <v>1966</v>
       </c>
       <c r="B5" t="n">
+        <v>107.58</v>
+      </c>
+      <c r="C5" t="n">
         <v>105.8</v>
-      </c>
-      <c r="C5" t="n">
-        <v>107.58</v>
       </c>
     </row>
     <row r="6">
@@ -679,10 +679,10 @@
         <v>1967</v>
       </c>
       <c r="B6" t="n">
+        <v>105.72</v>
+      </c>
+      <c r="C6" t="n">
         <v>106.53</v>
-      </c>
-      <c r="C6" t="n">
-        <v>105.72</v>
       </c>
     </row>
     <row r="7">
@@ -690,10 +690,10 @@
         <v>1968</v>
       </c>
       <c r="B7" t="n">
+        <v>108.17</v>
+      </c>
+      <c r="C7" t="n">
         <v>109.07</v>
-      </c>
-      <c r="C7" t="n">
-        <v>108.17</v>
       </c>
     </row>
     <row r="8">
@@ -701,10 +701,10 @@
         <v>1969</v>
       </c>
       <c r="B8" t="n">
+        <v>114.29</v>
+      </c>
+      <c r="C8" t="n">
         <v>112.65</v>
-      </c>
-      <c r="C8" t="n">
-        <v>114.29</v>
       </c>
     </row>
     <row r="9">
@@ -712,10 +712,10 @@
         <v>1970</v>
       </c>
       <c r="B9" t="n">
+        <v>115.89</v>
+      </c>
+      <c r="C9" t="n">
         <v>118.28</v>
-      </c>
-      <c r="C9" t="n">
-        <v>115.89</v>
       </c>
     </row>
     <row r="10">
@@ -723,10 +723,10 @@
         <v>1971</v>
       </c>
       <c r="B10" t="n">
+        <v>119.34</v>
+      </c>
+      <c r="C10" t="n">
         <v>123.21</v>
-      </c>
-      <c r="C10" t="n">
-        <v>119.34</v>
       </c>
     </row>
     <row r="11">
@@ -734,10 +734,10 @@
         <v>1972</v>
       </c>
       <c r="B11" t="n">
+        <v>127.37</v>
+      </c>
+      <c r="C11" t="n">
         <v>126.05</v>
-      </c>
-      <c r="C11" t="n">
-        <v>127.37</v>
       </c>
     </row>
     <row r="12">
@@ -745,10 +745,10 @@
         <v>1973</v>
       </c>
       <c r="B12" t="n">
+        <v>145.03</v>
+      </c>
+      <c r="C12" t="n">
         <v>128.47</v>
-      </c>
-      <c r="C12" t="n">
-        <v>145.03</v>
       </c>
     </row>
     <row r="13"/>
@@ -793,7 +793,7 @@
         <v>1965</v>
       </c>
       <c r="B18" t="n">
-        <v>102.67</v>
+        <v>103.06</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -816,7 +816,7 @@
         <v>1965</v>
       </c>
       <c r="B19" t="n">
-        <v>103.06</v>
+        <v>102.67</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -839,7 +839,7 @@
         <v>1966</v>
       </c>
       <c r="B20" t="n">
-        <v>105.8</v>
+        <v>107.58</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
         <v>1966</v>
       </c>
       <c r="B21" t="n">
-        <v>107.58</v>
+        <v>105.8</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>1967</v>
       </c>
       <c r="B22" t="n">
-        <v>106.53</v>
+        <v>105.72</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>1967</v>
       </c>
       <c r="B23" t="n">
-        <v>105.72</v>
+        <v>106.53</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>1968</v>
       </c>
       <c r="B24" t="n">
-        <v>109.07</v>
+        <v>108.17</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -954,7 +954,7 @@
         <v>1968</v>
       </c>
       <c r="B25" t="n">
-        <v>108.17</v>
+        <v>109.07</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>1969</v>
       </c>
       <c r="B26" t="n">
-        <v>112.65</v>
+        <v>114.29</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
         <v>1969</v>
       </c>
       <c r="B27" t="n">
-        <v>114.29</v>
+        <v>112.65</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>1970</v>
       </c>
       <c r="B28" t="n">
-        <v>118.28</v>
+        <v>115.89</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>1970</v>
       </c>
       <c r="B29" t="n">
-        <v>115.89</v>
+        <v>118.28</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         <v>1971</v>
       </c>
       <c r="B30" t="n">
-        <v>123.21</v>
+        <v>119.34</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>1971</v>
       </c>
       <c r="B31" t="n">
-        <v>119.34</v>
+        <v>123.21</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>1972</v>
       </c>
       <c r="B32" t="n">
-        <v>126.05</v>
+        <v>127.37</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>1972</v>
       </c>
       <c r="B33" t="n">
-        <v>127.37</v>
+        <v>126.05</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>1973</v>
       </c>
       <c r="B34" t="n">
-        <v>128.47</v>
+        <v>145.03</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
         <v>1973</v>
       </c>
       <c r="B35" t="n">
-        <v>145.03</v>
+        <v>128.47</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A144"/>
+  <dimension ref="A1:A162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1281,7 +1281,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>**Author**: opus-subagent-ch8-fanout</t>
+          <t>**Author**: Anu automated extraction pipeline</t>
         </is>
       </c>
     </row>
@@ -1298,14 +1298,14 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>&gt; Fig 8.1 (which reproduces Eichner 1973 p.1187) from the book PDF (Oxford print p413, found in Robert's</t>
+          <t>&gt; Fig 8.1 (which reproduces Eichner 1973 p.1187) from the book PDF (Oxford print p413, from the</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>&gt; `_PDF_LIBRARY`), **overlay-validated against the figure**. Two entities (Oligopolistic, Competitive),</t>
+          <t>&gt; project's PDF library), **overlay-validated against the figure**. Two entities (Oligopolistic, Competitive),</t>
         </is>
       </c>
     </row>
@@ -1402,7 +1402,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>## 1. Definition</t>
+          <t>&gt; **Reconciliation note (2026-06-11, ch8/9 pass):** Sections 1-9 below were authored when S801 was `data_unavailable` and have been rewritten to the **recovered** state (see the recovery header above). The historical data_unavailable language was internally inconsistent with the recovery header, the populated `chopped/S801.csv`, and the registry status `book_period_validated`.</t>
         </is>
       </c>
     </row>
@@ -1412,7 +1412,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>**S801** is Shaikh's Figure 8.1, a reproduction of Eichner (1973, *Economic Journal*, p. 1187): two wholesale-price-index lines (base 1957-59 = 100) for "concentrated" vs. "competitive" US industries, monthly/annual, **1965-1973**.</t>
+          <t>## 1. Definition</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Per the playbook recipe for `content_type = data_unavailable`:</t>
+          <t>**S801** is Shaikh's Figure 8.1, a reproduction of Eichner (1973, *Economic Journal*, p. 1187): two wholesale-price-index lines (base 1957-59 = 100) for "concentrated" (oligopolistic) vs. "competitive" US industries, annual, **1965-1973**. The series was recovered (2026-05-26) by offline vector extraction of Shaikh's reproduced figure and overlay-validated against it; provenance is `digitized` (digitization fidelity, not Eichner's exact unpublished table).</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>&gt; "DPR + EPR documenting the chart-only source and why no underlying data exists ... L01 returns SKIPPED ... V03 returns PASS_DATA_UNAVAILABLE ... No chopped CSV. Extenbook contains only the DPR + EPR + Source pages. Phase 8 viz uses the book figure image directly."</t>
+          <t>## 2. Why it matters in Chapter 8</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1442,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>## 2. Why it matters in Chapter 8</t>
+          <t>Section II.3 of Chapter 8 ("Price rigidity and monopoly power", pp. 371-373) frames Shaikh's critique of the administered-prices hypothesis. Eichner's chart is the opening exhibit: it shows that concentrated-industry wholesale prices were *smoother* than competitive-industry prices over 1965-1973 (including the Nixon Phase I / Phase II wage-price controls). Shaikh accepts the chart's empirical pattern but rejects the inferential leap to monopoly power, citing Stigler (1963, p. 70): smoother prices in concentrated sectors reflect higher fixed/entry costs, not higher trend profitability.</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Section II.3 of Chapter 8 ("Price rigidity and monopoly power", pp. 371-373) frames Shaikh's critique of the administered-prices hypothesis. Eichner's chart is the opening exhibit: it shows that concentrated-industry wholesale prices were *smoother* than competitive-industry prices over 1965-1973 (including the Nixon Phase I / Phase II wage-price controls). Shaikh accepts the chart's empirical pattern but rejects the inferential leap to monopoly power, citing Stigler (1963, p. 70): smoother prices in concentrated sectors reflect higher fixed/entry costs, not higher trend profitability.</t>
+          <t>## 3. Sources</t>
         </is>
       </c>
     </row>
@@ -1462,113 +1462,113 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>## 3. Sources</t>
+          <t>| Subseries | Coverage | Publisher | Status |</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr"/>
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>|---|---|---|---|</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>| Subseries | Coverage | Publisher | Status |</t>
+          <t>| S801-A-Oligopolistic | 1965-1973 | EICHNER_1973_EJ (via Shaikh Fig 8.1) | book_period_validated |</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>|---|---|---|---|</t>
+          <t>| S801-A-Competitive | 1965-1973 | EICHNER_1973_EJ (via Shaikh Fig 8.1) | book_period_validated |</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>| (none — chart-only) | 1965-1973 | EICHNER_1973_FIG8_1 | **data_unavailable** |</t>
-        </is>
-      </c>
+      <c r="A46" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr"/>
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Eichner 1973, Economic Journal 83(332), p. 1187 publishes Figure 8.1 as a **chart only**; there is no underlying table in the source publication, and Shaikh (2016, p. 372) transcribes no numeric values in the narrative. Because the chart is the authoritative record, the values were recovered by **offline vector extraction of Shaikh's reproduced figure** (Oxford print p. 413, from the project's PDF library) and overlay-validated against the figure. Provenance is therefore `digitized`. The recovered source workbook is `SalvagedInputs/book_data/Reconstructed/Eichner_1973_Fig8_1_S801.xlsx`.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Eichner 1973, Economic Journal 83(332), p. 1187 publishes Figure 8.1 as a chart only. There is no underlying table in the source publication. The Eichner 1973 PDF is not present in `Inputs/` or `Technical/data/raw/01_SOURCE_MATERIALS/` of the RSCD workspace (Phase 5 blocker-resolver searched and confirmed). Shaikh (2016) reproduces the chart on book p. 372 but transcribes no numeric values in the narrative. The `SalvagedInputs/book_data/ShaikhChoppedTables/Appendix8_*.xlsx` set tabulates Figures 8.2-8.6 but contains no file for Eichner Fig 8.1.</t>
-        </is>
-      </c>
+      <c r="A48" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr"/>
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>## 4. Construction</t>
+        </is>
+      </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Phase 5 blocker B6 was formally resolved as `data_unavailable` (research dossier review_history entry, 2026-05-18).</t>
-        </is>
-      </c>
+      <c r="A50" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr"/>
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>`construction: direct` (digitized reproduction of Shaikh's chart):</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>## 4. Construction</t>
+          <t>- `L01_S801.py` loads the recovered Eichner_1973_Fig8_1 workbook (two index lines, 1965-1973).</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr"/>
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>- `V03_S801.py` round-trip validates against the source workbook (PASS, n=18, MAE 0.0).</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>N/A. No data file exists for the loader to ingest. Per the playbook:</t>
+          <t>- Chopped CSV present at `Technical/chopped/S801.csv` (18 rows: 9 years x 2 entities).</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>- `L01_S801_load.py` returns `{"status": "SKIPPED", "reason": "data_unavailable"}`.</t>
+          <t>- Two entities captured: Oligopolistic (concentrated) reaching ~145 by 1973 vs. Competitive (unconcentrated) reaching ~128.5 — the late administered-price divergence.</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>- `P02_S801_construct.py` is not authored.</t>
-        </is>
-      </c>
+      <c r="A56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>- `V03_S801_validate.py` returns `{"status": "PASS_DATA_UNAVAILABLE"}`.</t>
+          <t>## 5. Year coverage</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>- No chopped CSV at `Technical/chopped/S801.csv`.</t>
-        </is>
-      </c>
+      <c r="A58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>- No processed parquet at `Technical/data/processed/S801.parquet`.</t>
+          <t>- **Book period**: 1965-1973 (annual, per chart)</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>- Phase 9 visualization uses the book figure image directly (no digitization in Phase 5).</t>
+          <t>- **Extension period**: not applicable (extension would be a proxy substitution; see caveat 3)</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>## 5. Year coverage</t>
+          <t>## 6. Units</t>
         </is>
       </c>
     </row>
@@ -1588,228 +1588,236 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>- **Book period**: 1965-1973 (annual, per chart)</t>
+          <t>Wholesale price index, base 1957-59 = 100 (per Eichner's chart axis).</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>- **Extension period**: not applicable (data_unavailable; see EPR §1 and §2)</t>
-        </is>
-      </c>
+      <c r="A65" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr"/>
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>## 7. Caveats</t>
+        </is>
+      </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>## 6. Units</t>
-        </is>
-      </c>
+      <c r="A67" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr"/>
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>1. **Digitized provenance, not Eichner's exact table.** Eichner 1973 published Figure 8.1 as a chart with no underlying table; the published chart (as reproduced by Shaikh) is the authoritative record. The recovered values carry digitization fidelity (overlay-validated), not transcription fidelity.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Wholesale price index, base 1957-59 = 100 (per Eichner's chart axis).</t>
+          <t>2. **A BLS PPI reconstruction would be a proxy substitution.** The Adequacy Report's extension_candidates (BLS PPI by NAICS industry, partitioned by Census Concentration Ratios) require SIC-&gt;NAICS concordance and re-application of the high-CR / low-CR partition. The set of industries in Eichner's 1965-1973 "concentrated" and "competitive" aggregates is itself unrecoverable, so any modern reconstruction would be a proxy in the Anu sense (formal Concept Match Justification required). Not attempted.</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr"/>
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>3. **Stub-name correction.** S801 was renamed from the stale "US Long-Run Interest Rates and Prices" (a carryover from CD2 S042, which is a Chapter 10 series). `cd2_id` was nulled in Phase 3.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>## 7. Caveats</t>
-        </is>
-      </c>
+      <c r="A71" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr"/>
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>## 8. Cross-references</t>
+        </is>
+      </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>1. **No byte-exact reproduction possible** from local materials. Eichner 1973 published Figure 8.1 as a chart with no underlying table; Shaikh did not transcribe values; the Appendix8_* chopped tables do not include this figure. The published Eichner chart stands as the authoritative record.</t>
-        </is>
-      </c>
+      <c r="A73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2. **WebPlotDigitizer is out of scope for Phase 5.** Even if the Eichner 1973 PDF were obtained from JSTOR (DOI 10.2307/2230843), digitizing the chart would introduce non-trivial sampling noise and would conflict with the Anu No-Synthetic rule for primary data ingestion. Digitization is appropriately constrained as a Phase 9 visualization task (with `provenance: digitized` flagging).</t>
+          <t>- **CD legacy ID**: `S042` (predecessor link; CD2 mismap — CD2 S042 is a Ch10 interest rate series, not a true predecessor for Ch8 Fig 8.1)</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>3. **BLS PPI reconstruction would be a proxy substitution.** The Adequacy Report's extension_candidates (BLS PPI by NAICS industry, partitioned by Census Concentration Ratios) require SIC-&gt;NAICS concordance and a re-application of the high-CR / low-CR partition. The set of industries in Eichner's 1965-1973 "concentrated" and "competitive" aggregates is itself unrecoverable. Any modern reconstruction would therefore be a proxy in the Anu sense, requiring formal Concept Match Justification in an EPR. Not attempted in Phase 5.</t>
+          <t>- **CD2 legacy ID**: null (no genuine CD2 predecessor)</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>4. **Stub-name correction.** S801 was renamed from the stale "US Long-Run Interest Rates and Prices" (a carryover from CD2 S042, which is a Chapter 10 series). `cd2_id` was nulled in Phase 3.</t>
+          <t>- **Book reference**: Shaikh (2016), Ch. 8, p. 372 (text + Fig 8.1)</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr"/>
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>- **Originating publication**: Eichner, Alfred S. (1973), "A Theory of the Determination of the Mark-Up Under Oligopoly," *Economic Journal* 83(332): 1184-1200. DOI: 10.2307/2230843. Wayback fallback confirmed HTTP 200.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>## 8. Cross-references</t>
-        </is>
-      </c>
+      <c r="A78" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr"/>
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>## 9. Validation expectation</t>
+        </is>
+      </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>- **CD legacy ID**: `S042` (predecessor link; CD2 mismap — CD2 S042 is a Ch10 interest rate series, not a true predecessor for Ch8 Fig 8.1)</t>
-        </is>
-      </c>
+      <c r="A80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>- **CD2 legacy ID**: null (no genuine CD2 predecessor)</t>
+          <t>- **Status**: `PASS` (round-trip against the recovered Eichner_1973_Fig8_1 workbook; n=18, MAE 0.0).</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>- **Book reference**: Shaikh (2016), Ch. 8, p. 372 (text + Fig 8.1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>- **Originating publication**: Eichner, Alfred S. (1973), "A Theory of the Determination of the Mark-Up Under Oligopoly," *Economic Journal* 83(332): 1184-1200. DOI: 10.2307/2230843. Wayback fallback confirmed HTTP 200.</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr"/>
+          <t>- Provenance flag: `digitized` (figure-overlay validated, not Eichner's unpublished table).</t>
+        </is>
+      </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>## 9. Validation expectation</t>
-        </is>
+      <c r="A85" s="4">
+        <f>== EPR: S801_EPR.md ===</f>
+        <v/>
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr"/>
+      <c r="A86" t="inlineStr">
+        <is>
+          <t># S801 — Extension Provenance Record</t>
+        </is>
+      </c>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>- **Status**: `PASS_DATA_UNAVAILABLE` (per playbook).</t>
-        </is>
-      </c>
+      <c r="A87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>- No tolerance applies; the validator records that no underlying data exists in the workspace and that this is the intended state.</t>
+          <t>**Series**: S801 — Wholesale Prices in Oligopolistic and Competitive Industries, 1965-1973 (Eichner Fig 8.1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>**Phase**: 6 (Extension)</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>**Construction classification**: `direct` (digitized reproduction of Shaikh's Figure 8.1)</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="4">
-        <f>== EPR: S801_EPR.md ===</f>
-        <v/>
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>**Extension method**: not applicable — a modern reconstruction would be a proxy, see §2</t>
+        </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t># S801 — Extension Provenance Record</t>
+          <t>**Authored**: 2026-05-18 · **Recovery update**: 2026-05-26</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr"/>
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>**Author**: Anu automated extraction pipeline</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>**Series**: S801 — Wholesale Prices in Oligopolistic and Competitive Industries, 1965-1973 (Eichner Fig 8.1)</t>
+          <t>**Related**: `S801_DPR.md`</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>**Phase**: 6 (Extension)</t>
-        </is>
-      </c>
+      <c r="A95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>**Construction classification**: `data_unavailable`</t>
+          <t>---</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>**Extension method**: not applicable — see §1</t>
-        </is>
-      </c>
+      <c r="A97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>**Authored**: 2026-05-18</t>
+          <t>&gt; **Recovery (2026-05-26):** This record was originally authored when S801 was `data_unavailable`.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>**Author**: opus-subagent-ch8-fanout</t>
+          <t>&gt; S801 was subsequently **recovered by figure digitization**: an offline native-vector trace of Shaikh's</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>**Related**: `S801_DPR.md`</t>
+          <t>&gt; Figure 8.1 (which reproduces Eichner 1973, p. 1187) from the book PDF, overlay-validated against the</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr"/>
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>&gt; figure. The series now carries two index lines (Oligopolistic, Competitive), 1965-1973, base 1957-59 = 100,</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>&gt; with `provenance: digitized` (digitization fidelity, not Eichner's exact unpublished table). Round-trip</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" t="inlineStr"/>
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>&gt; validation PASS (n=18, MAE 0.0). The sections below have been rewritten to the recovered state; the earlier</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>## 1. Classification</t>
+          <t>&gt; `data_unavailable` framing was superseded by the recovery.</t>
         </is>
       </c>
     </row>
@@ -1819,7 +1827,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>`content_type = data_unavailable`. There is no byte-exact underlying dataset to extend. Eichner (1973) p. 1187 publishes Figure 8.1 as a chart only; no underlying table accompanies the chart; Shaikh (2016) reproduces the chart without transcribing values; the Appendix8_* chopped tables do not include this figure (only Figs 8.2-8.6).</t>
+          <t>## 1. Classification</t>
         </is>
       </c>
     </row>
@@ -1829,31 +1837,31 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>## 2. Why no extension is attempted</t>
+          <t>`content_type = time_series` (two annual index lines, 1965-1973), `construction = direct`. The book-period</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" t="inlineStr"/>
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>data now exists as a digitized reproduction of Shaikh's Figure 8.1 and is byte-stable against its recovered</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>- The original raw data (Eichner's 1965-1973 wholesale-price indices for his specific concentrated vs. competitive industry partition) is not available in any source accessible to the RSCD workspace.</t>
+          <t>source workbook. There is, however, no faithful modern **extension** — see §2.</t>
         </is>
       </c>
     </row>
     <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>- The closest modern source (BLS PPI by NAICS industry, partitioned via Census Concentration Ratios) has incompatible industry classifications (SIC 1965-1973 vs. NAICS post-1997), and the set of industries in Eichner's specific high-CR / low-CR partition is itself unrecoverable.</t>
-        </is>
-      </c>
+      <c r="A111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>- Any modern reconstruction would therefore be a proxy in the Anu sense, requiring formal Concept Match Justification and Phase 6 human review approval. Per the Anti-Degradation and No-Proxy rules, this is not undertaken in Phase 5.</t>
+          <t>## 2. Why no extension is attempted</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1871,63 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>## 3. Method</t>
+          <t>- Eichner (1973, p. 1187) published Figure 8.1 as a **chart only**; there is no underlying table, and the</t>
         </is>
       </c>
     </row>
     <row r="115">
-      <c r="A115" t="inlineStr"/>
+      <c r="A115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  specific set of industries in Eichner's 1965-1973 "concentrated" and "competitive" aggregates is not</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>N/A.</t>
+          <t xml:space="preserve">  recoverable from the published article.</t>
         </is>
       </c>
     </row>
     <row r="117">
-      <c r="A117" t="inlineStr"/>
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>- The closest modern source (US producer-price indices by industry, partitioned by Census concentration</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>## 4. No-Proxy disclosure</t>
+          <t xml:space="preserve">  ratios) uses incompatible industry classifications (1965-1973 SIC codes vs. post-1997 NAICS) and would</t>
         </is>
       </c>
     </row>
     <row r="119">
-      <c r="A119" t="inlineStr"/>
+      <c r="A119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  require re-selecting an industry set to mirror Eichner's — which is itself unrecoverable.</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>**None attempted.** BLS PPI is not a proxy for Eichner's chart — it would be a *re-construction* requiring (a) SIC→NAICS concordance, (b) re-application of CR thresholds, and (c) selection of an industry set that mirrors Eichner's (which itself is unrecoverable from the published article). Such a reconstruction would not meet the Anu No-Proxy bar without explicit Phase 6 human review.</t>
+          <t>- Any modern continuation would therefore be a **proxy reconstruction**, not a faithful extension of the</t>
         </is>
       </c>
     </row>
     <row r="121">
-      <c r="A121" t="inlineStr"/>
+      <c r="A121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  original figure. Under the no-proxy and no-synthetic rules this is not undertaken; it would be a new</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>## 5. No-Synthetic disclosure</t>
+          <t xml:space="preserve">  series requiring an explicit concept-match justification and human review.</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1937,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>**None.** No interpolation, no digitization (digitization deferred to Phase 9 visualization, where it is appropriately constrained with `provenance: digitized` flagging).</t>
+          <t>## 3. Method</t>
         </is>
       </c>
     </row>
@@ -1923,59 +1947,55 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>## 6. Failure-mode table</t>
+          <t>The book-period values are a digitized reproduction (native-vector figure trace, overlay-validated). No</t>
         </is>
       </c>
     </row>
     <row r="127">
-      <c r="A127" t="inlineStr"/>
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>extension method is applied.</t>
+        </is>
+      </c>
     </row>
     <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>| Failure | Action |</t>
-        </is>
-      </c>
+      <c r="A128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>|---|---|</t>
+          <t>## 4. No-Proxy disclosure</t>
         </is>
       </c>
     </row>
     <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>| Loader invoked | Returns `{"status": "SKIPPED", "reason": "data_unavailable"}` — by design, not a failure |</t>
-        </is>
-      </c>
+      <c r="A130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>| Processor invoked | Not authored — no `P02_S801_construct.py` |</t>
+          <t>**No proxy used.** A modern producer-price reconstruction is *not* a proxy for Eichner's chart — it would be</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>| Validator invoked | Returns `{"status": "PASS_DATA_UNAVAILABLE"}` |</t>
+          <t>a re-construction requiring (a) a SIC-to-NAICS concordance, (b) re-application of concentration thresholds,</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>| Chopped writer invoked | No `Technical/data/processed/S801.parquet` exists; writer silently passes |</t>
+          <t>and (c) selection of an industry set mirroring Eichner's (itself unrecoverable). Such a reconstruction would</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>| Extenbook writer invoked | No processed parquet → no extenbook by default; manual extenbook (DPR + EPR + Source pages only) may be authored later if needed |</t>
+          <t>not meet the no-proxy bar without explicit human review.</t>
         </is>
       </c>
     </row>
@@ -1985,7 +2005,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>## 7. CD2 divergence pre-disclosure</t>
+          <t>## 5. No-Synthetic disclosure</t>
         </is>
       </c>
     </row>
@@ -1995,41 +2015,151 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>CD2 had no genuine per-series CSV that matches this exhibit's content. The stub's `cd2_id = S042` was a stale carryover from a Ch10 interest-rate series and has been nulled. The CD2-vs-RSCD comparison is not meaningful here.</t>
+          <t>**None.** The book-period values are recovered by figure digitization (overlay-validated), not interpolated,</t>
         </is>
       </c>
     </row>
     <row r="139">
-      <c r="A139" t="inlineStr"/>
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>extrapolated, or synthetically generated. Digitization fidelity is flagged with `provenance: digitized`.</t>
+        </is>
+      </c>
     </row>
     <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>## 8. Recovery paths (out-of-scope for Phase 6)</t>
-        </is>
-      </c>
+      <c r="A140" t="inlineStr"/>
     </row>
     <row r="141">
-      <c r="A141" t="inlineStr"/>
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>## 6. Failure-mode table</t>
+        </is>
+      </c>
     </row>
     <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>1. **Obtain Eichner 1973 EJ PDF** from JSTOR (DOI 10.2307/2230843; institutional access required — Wayback fallback confirmed HTTP 200) and run WebPlotDigitizer on Figure 8.1 to extract (date, concentrated_index, competitive_index) samples. This would be a **Phase 9 visualization task** with explicit `provenance: digitized` flagging, not a Phase 5 data-ingestion task.</t>
-        </is>
-      </c>
+      <c r="A142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2. **Author contact**: Alfred Eichner died in 1988; his archived working papers may contain the underlying spreadsheet. Out of scope for the current pipeline.</t>
+          <t>| Failure | Action |</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>3. **BLS PPI reconstruction**: would be a NEW series (e.g., S801b), classified as a proxy substitution per Anu Framework, requiring Phase 6 formal review and a Concept Match Justification. Out of scope for the current pipeline.</t>
+          <t>|---|---|</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>| Loader cannot find recovered source workbook | Returns `{"status": "FAIL", "reason": "source_missing"}` |</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>| Round-trip divergence against recovered workbook | FAIL — investigate the digitized workbook vs. the figure trace |</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>| Extension requested | Not applicable — a modern reconstruction would be a proxy (see §2) |</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>## 7. Predecessor divergence pre-disclosure</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>No genuine predecessor per-series dataset matches this exhibit's content. The stub's earlier `S042` link was a</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>stale carryover from a Chapter 10 interest-rate series and has been nulled. A predecessor comparison is not</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>meaningful here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>## 8. Recovery record and future work</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>1. **Recovered (2026-05-26)**: native-vector trace of Shaikh's Figure 8.1 from the book PDF, overlay-validated,</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   `provenance: digitized`. This is the current state of the series.</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2. **Author's underlying spreadsheet** (out of scope): Alfred Eichner died in 1988; archived working papers may</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   contain the original values, but these are not accessible to this project.</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>3. **Modern producer-price reconstruction** (out of scope): would be a NEW series classified as a proxy</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   substitution, requiring a formal concept-match justification and human review — not an extension of S801.</t>
         </is>
       </c>
     </row>
@@ -2275,7 +2405,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-05-26T21:40:03.605029+00:00</t>
+          <t>2026-07-10T13:13:05.659471+00:00</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S801_extenbook.xlsx
+++ b/extenbooks/S801_extenbook.xlsx
@@ -1214,7 +1214,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A162"/>
+  <dimension ref="A1:A164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1312,14 +1312,14 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>&gt; 1965-1973, index 1957-59=100 — captures the late administered-price divergence (olig→145 vs comp→128.5</t>
+          <t>&gt; 1965-1973, index 1957-59=100 — captures the late administered-price divergence (comp→145 vs olig→128.5</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>&gt; by 1973). `provenance: digitized` (digitization fidelity, not Eichner's exact table). Pipeline:</t>
+          <t>&gt; by 1973; the smooth/administered line is the *oligopolistic* one). `provenance: digitized` (digitization fidelity, not Eichner's exact table). Pipeline:</t>
         </is>
       </c>
     </row>
@@ -1407,12 +1407,16 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr"/>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>## 1. Definition</t>
+          <t>&gt; **Label-transposition correction (2026-07-10, F-T2-01):** The 2026-05-26 digitization baked the two industry columns in *backwards* — the volatile, spiking line (terminal 145.03) had been labeled **Oligopolistic** and the smooth/administered line (terminal 128.47) **Competitive**, the inverse of Shaikh Fig 8.1 (the concentrated/oligopolistic line is the *smoother* one — Shaikh p.372: "the smoother prices of the concentrated industries"; figure legend: solid = Competitive, dashed = Oligopolistic). Corrected at the loader (`L01_S801.py` relabels the frozen source columns; values unchanged), with V03 applying the same relabel to the truth xlsx **and** a new independent variance sanity check (var(Competitive) &gt; var(Oligopolistic)). After correction: **Competitive → 145.03, Oligopolistic → 128.47** at 1973. See `Technical/anu_framework_review/F-T2-01.md` and `Technical/remediation_v16/evidence/P1.2_S801.md`.</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1426,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>**S801** is Shaikh's Figure 8.1, a reproduction of Eichner (1973, *Economic Journal*, p. 1187): two wholesale-price-index lines (base 1957-59 = 100) for "concentrated" (oligopolistic) vs. "competitive" US industries, annual, **1965-1973**. The series was recovered (2026-05-26) by offline vector extraction of Shaikh's reproduced figure and overlay-validated against it; provenance is `digitized` (digitization fidelity, not Eichner's exact unpublished table).</t>
+          <t>## 1. Definition</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1436,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>## 2. Why it matters in Chapter 8</t>
+          <t>**S801** is Shaikh's Figure 8.1, a reproduction of Eichner (1973, *Economic Journal*, p. 1187): two wholesale-price-index lines (base 1957-59 = 100) for "concentrated" (oligopolistic) vs. "competitive" US industries, annual, **1965-1973**. The series was recovered (2026-05-26) by offline vector extraction of Shaikh's reproduced figure and overlay-validated against it; provenance is `digitized` (digitization fidelity, not Eichner's exact unpublished table).</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1446,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Section II.3 of Chapter 8 ("Price rigidity and monopoly power", pp. 371-373) frames Shaikh's critique of the administered-prices hypothesis. Eichner's chart is the opening exhibit: it shows that concentrated-industry wholesale prices were *smoother* than competitive-industry prices over 1965-1973 (including the Nixon Phase I / Phase II wage-price controls). Shaikh accepts the chart's empirical pattern but rejects the inferential leap to monopoly power, citing Stigler (1963, p. 70): smoother prices in concentrated sectors reflect higher fixed/entry costs, not higher trend profitability.</t>
+          <t>## 2. Why it matters in Chapter 8</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1456,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>## 3. Sources</t>
+          <t>Section II.3 of Chapter 8 ("Price rigidity and monopoly power", pp. 371-373) frames Shaikh's critique of the administered-prices hypothesis. Eichner's chart is the opening exhibit: it shows that concentrated-industry wholesale prices were *smoother* than competitive-industry prices over 1965-1973 (including the Nixon Phase I / Phase II wage-price controls). Shaikh accepts the chart's empirical pattern but rejects the inferential leap to monopoly power, citing Stigler (1963, p. 70): smoother prices in concentrated sectors reflect higher fixed/entry costs, not higher trend profitability.</t>
         </is>
       </c>
     </row>
@@ -1462,38 +1466,38 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>| Subseries | Coverage | Publisher | Status |</t>
+          <t>## 3. Sources</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>|---|---|---|---|</t>
-        </is>
-      </c>
+      <c r="A43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>| S801-A-Oligopolistic | 1965-1973 | EICHNER_1973_EJ (via Shaikh Fig 8.1) | book_period_validated |</t>
+          <t>| Subseries | Coverage | Publisher | Status |</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>| S801-A-Competitive | 1965-1973 | EICHNER_1973_EJ (via Shaikh Fig 8.1) | book_period_validated |</t>
+          <t>|---|---|---|---|</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr"/>
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>| S801-A-Oligopolistic | 1965-1973 | EICHNER_1973_EJ (via Shaikh Fig 8.1) | book_period_validated |</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Eichner 1973, Economic Journal 83(332), p. 1187 publishes Figure 8.1 as a **chart only**; there is no underlying table in the source publication, and Shaikh (2016, p. 372) transcribes no numeric values in the narrative. Because the chart is the authoritative record, the values were recovered by **offline vector extraction of Shaikh's reproduced figure** (Oxford print p. 413, from the project's PDF library) and overlay-validated against the figure. Provenance is therefore `digitized`. The recovered source workbook is `SalvagedInputs/book_data/Reconstructed/Eichner_1973_Fig8_1_S801.xlsx`.</t>
+          <t>| S801-A-Competitive | 1965-1973 | EICHNER_1973_EJ (via Shaikh Fig 8.1) | book_period_validated |</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1507,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>## 4. Construction</t>
+          <t>Eichner 1973, Economic Journal 83(332), p. 1187 publishes Figure 8.1 as a **chart only**; there is no underlying table in the source publication, and Shaikh (2016, p. 372) transcribes no numeric values in the narrative. Because the chart is the authoritative record, the values were recovered by **offline vector extraction of Shaikh's reproduced figure** (Oxford print p. 413, from the project's PDF library) and overlay-validated against the figure. Provenance is therefore `digitized`. The recovered source workbook is `SalvagedInputs/book_data/Reconstructed/Eichner_1973_Fig8_1_S801.xlsx`.</t>
         </is>
       </c>
     </row>
@@ -1513,45 +1517,45 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>`construction: direct` (digitized reproduction of Shaikh's chart):</t>
+          <t>## 4. Construction</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>- `L01_S801.py` loads the recovered Eichner_1973_Fig8_1 workbook (two index lines, 1965-1973).</t>
-        </is>
-      </c>
+      <c r="A52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>- `V03_S801.py` round-trip validates against the source workbook (PASS, n=18, MAE 0.0).</t>
+          <t>`construction: direct` (digitized reproduction of Shaikh's chart):</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>- Chopped CSV present at `Technical/chopped/S801.csv` (18 rows: 9 years x 2 entities).</t>
+          <t>- `L01_S801.py` loads the recovered Eichner_1973_Fig8_1 workbook (two index lines, 1965-1973).</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>- Two entities captured: Oligopolistic (concentrated) reaching ~145 by 1973 vs. Competitive (unconcentrated) reaching ~128.5 — the late administered-price divergence.</t>
+          <t>- `V03_S801.py` round-trip validates against the source workbook (PASS, n=18, MAE 0.0).</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr"/>
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>- Chopped CSV present at `Technical/chopped/S801.csv` (18 rows: 9 years x 2 entities).</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>## 5. Year coverage</t>
+          <t>- Two entities captured: Competitive (unconcentrated) — the volatile line — reaching ~145 by 1973 vs. Oligopolistic (concentrated) — the smooth/administered line — reaching ~128.5. This is the late administered-price divergence: the *concentrated* line is the smoother one (Shaikh p.372: "the smoother prices of the concentrated industries"), not the higher-reaching one.</t>
         </is>
       </c>
     </row>
@@ -1561,24 +1565,24 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
+          <t>## 5. Year coverage</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
           <t>- **Book period**: 1965-1973 (annual, per chart)</t>
         </is>
       </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>- **Extension period**: not applicable (extension would be a proxy substitution; see caveat 3)</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>## 6. Units</t>
+          <t>- **Extension period**: not applicable (extension would be a proxy substitution; see caveat 3)</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1592,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Wholesale price index, base 1957-59 = 100 (per Eichner's chart axis).</t>
+          <t>## 6. Units</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1602,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>## 7. Caveats</t>
+          <t>Wholesale price index, base 1957-59 = 100 (per Eichner's chart axis).</t>
         </is>
       </c>
     </row>
@@ -1608,31 +1612,31 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1. **Digitized provenance, not Eichner's exact table.** Eichner 1973 published Figure 8.1 as a chart with no underlying table; the published chart (as reproduced by Shaikh) is the authoritative record. The recovered values carry digitization fidelity (overlay-validated), not transcription fidelity.</t>
+          <t>## 7. Caveats</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>2. **A BLS PPI reconstruction would be a proxy substitution.** The Adequacy Report's extension_candidates (BLS PPI by NAICS industry, partitioned by Census Concentration Ratios) require SIC-&gt;NAICS concordance and re-application of the high-CR / low-CR partition. The set of industries in Eichner's 1965-1973 "concentrated" and "competitive" aggregates is itself unrecoverable, so any modern reconstruction would be a proxy in the Anu sense (formal Concept Match Justification required). Not attempted.</t>
-        </is>
-      </c>
+      <c r="A69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>3. **Stub-name correction.** S801 was renamed from the stale "US Long-Run Interest Rates and Prices" (a carryover from CD2 S042, which is a Chapter 10 series). `cd2_id` was nulled in Phase 3.</t>
+          <t>1. **Digitized provenance, not Eichner's exact table.** Eichner 1973 published Figure 8.1 as a chart with no underlying table; the published chart (as reproduced by Shaikh) is the authoritative record. The recovered values carry digitization fidelity (overlay-validated), not transcription fidelity.</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr"/>
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2. **A BLS PPI reconstruction would be a proxy substitution.** The Adequacy Report's extension_candidates (BLS PPI by NAICS industry, partitioned by Census Concentration Ratios) require SIC-&gt;NAICS concordance and re-application of the high-CR / low-CR partition. The set of industries in Eichner's 1965-1973 "concentrated" and "competitive" aggregates is itself unrecoverable, so any modern reconstruction would be a proxy in the Anu sense (formal Concept Match Justification required). Not attempted.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>## 8. Cross-references</t>
+          <t>3. **Stub-name correction.** S801 was renamed from the stale "US Long-Run Interest Rates and Prices" (a carryover from CD2 S042, which is a Chapter 10 series). `cd2_id` was nulled in Phase 3.</t>
         </is>
       </c>
     </row>
@@ -1642,38 +1646,38 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>- **CD legacy ID**: `S042` (predecessor link; CD2 mismap — CD2 S042 is a Ch10 interest rate series, not a true predecessor for Ch8 Fig 8.1)</t>
+          <t>## 8. Cross-references</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>- **CD2 legacy ID**: null (no genuine CD2 predecessor)</t>
-        </is>
-      </c>
+      <c r="A75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>- **Book reference**: Shaikh (2016), Ch. 8, p. 372 (text + Fig 8.1)</t>
+          <t>- **CD legacy ID**: `S042` (predecessor link; CD2 mismap — CD2 S042 is a Ch10 interest rate series, not a true predecessor for Ch8 Fig 8.1)</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>- **Originating publication**: Eichner, Alfred S. (1973), "A Theory of the Determination of the Mark-Up Under Oligopoly," *Economic Journal* 83(332): 1184-1200. DOI: 10.2307/2230843. Wayback fallback confirmed HTTP 200.</t>
+          <t>- **CD2 legacy ID**: null (no genuine CD2 predecessor)</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr"/>
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>- **Book reference**: Shaikh (2016), Ch. 8, p. 372 (text + Fig 8.1)</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>## 9. Validation expectation</t>
+          <t>- **Originating publication**: Eichner, Alfred S. (1973), "A Theory of the Determination of the Mark-Up Under Oligopoly," *Economic Journal* 83(332): 1184-1200. DOI: 10.2307/2230843. Wayback fallback confirmed HTTP 200.</t>
         </is>
       </c>
     </row>
@@ -1683,89 +1687,89 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
+          <t>## 9. Validation expectation</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
           <t>- **Status**: `PASS` (round-trip against the recovered Eichner_1973_Fig8_1 workbook; n=18, MAE 0.0).</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
+    <row r="84">
+      <c r="A84" t="inlineStr">
         <is>
           <t>- Provenance flag: `digitized` (figure-overlay validated, not Eichner's unpublished table).</t>
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="4">
+    <row r="87">
+      <c r="A87" s="4">
         <f>== EPR: S801_EPR.md ===</f>
         <v/>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t># S801 — Extension Provenance Record</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr"/>
-    </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>**Series**: S801 — Wholesale Prices in Oligopolistic and Competitive Industries, 1965-1973 (Eichner Fig 8.1)</t>
+          <t># S801 — Extension Provenance Record</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>**Phase**: 6 (Extension)</t>
-        </is>
-      </c>
+      <c r="A89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>**Construction classification**: `direct` (digitized reproduction of Shaikh's Figure 8.1)</t>
+          <t>**Series**: S801 — Wholesale Prices in Oligopolistic and Competitive Industries, 1965-1973 (Eichner Fig 8.1)</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>**Extension method**: not applicable — a modern reconstruction would be a proxy, see §2</t>
+          <t>**Phase**: 6 (Extension)</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>**Authored**: 2026-05-18 · **Recovery update**: 2026-05-26</t>
+          <t>**Construction classification**: `direct` (digitized reproduction of Shaikh's Figure 8.1)</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>**Author**: Anu automated extraction pipeline</t>
+          <t>**Extension method**: not applicable — a modern reconstruction would be a proxy, see §2</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>**Related**: `S801_DPR.md`</t>
+          <t>**Authored**: 2026-05-18 · **Recovery update**: 2026-05-26</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr"/>
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>**Author**: Anu automated extraction pipeline</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>**Related**: `S801_DPR.md`</t>
         </is>
       </c>
     </row>
@@ -1775,59 +1779,59 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>&gt; **Recovery (2026-05-26):** This record was originally authored when S801 was `data_unavailable`.</t>
+          <t>---</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>&gt; S801 was subsequently **recovered by figure digitization**: an offline native-vector trace of Shaikh's</t>
-        </is>
-      </c>
+      <c r="A99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>&gt; Figure 8.1 (which reproduces Eichner 1973, p. 1187) from the book PDF, overlay-validated against the</t>
+          <t>&gt; **Recovery (2026-05-26):** This record was originally authored when S801 was `data_unavailable`.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>&gt; figure. The series now carries two index lines (Oligopolistic, Competitive), 1965-1973, base 1957-59 = 100,</t>
+          <t>&gt; S801 was subsequently **recovered by figure digitization**: an offline native-vector trace of Shaikh's</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>&gt; with `provenance: digitized` (digitization fidelity, not Eichner's exact unpublished table). Round-trip</t>
+          <t>&gt; Figure 8.1 (which reproduces Eichner 1973, p. 1187) from the book PDF, overlay-validated against the</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>&gt; validation PASS (n=18, MAE 0.0). The sections below have been rewritten to the recovered state; the earlier</t>
+          <t>&gt; figure. The series now carries two index lines (Oligopolistic, Competitive), 1965-1973, base 1957-59 = 100,</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>&gt; `data_unavailable` framing was superseded by the recovery.</t>
+          <t>&gt; with `provenance: digitized` (digitization fidelity, not Eichner's exact unpublished table). Round-trip</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" t="inlineStr"/>
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>&gt; validation PASS (n=18, MAE 0.0). The sections below have been rewritten to the recovered state; the earlier</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>## 1. Classification</t>
+          <t>&gt; `data_unavailable` framing was superseded by the recovery.</t>
         </is>
       </c>
     </row>
@@ -1837,31 +1841,31 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>`content_type = time_series` (two annual index lines, 1965-1973), `construction = direct`. The book-period</t>
+          <t>## 1. Classification</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>data now exists as a digitized reproduction of Shaikh's Figure 8.1 and is byte-stable against its recovered</t>
-        </is>
-      </c>
+      <c r="A109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>source workbook. There is, however, no faithful modern **extension** — see §2.</t>
+          <t>`content_type = time_series` (two annual index lines, 1965-1973), `construction = direct`. The book-period</t>
         </is>
       </c>
     </row>
     <row r="111">
-      <c r="A111" t="inlineStr"/>
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>data now exists as a digitized reproduction of Shaikh's Figure 8.1 and is byte-stable against its recovered</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>## 2. Why no extension is attempted</t>
+          <t>source workbook. There is, however, no faithful modern **extension** — see §2.</t>
         </is>
       </c>
     </row>
@@ -1871,73 +1875,73 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>- Eichner (1973, p. 1187) published Figure 8.1 as a **chart only**; there is no underlying table, and the</t>
+          <t>## 2. Why no extension is attempted</t>
         </is>
       </c>
     </row>
     <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  specific set of industries in Eichner's 1965-1973 "concentrated" and "competitive" aggregates is not</t>
-        </is>
-      </c>
+      <c r="A115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t xml:space="preserve">  recoverable from the published article.</t>
+          <t>- Eichner (1973, p. 1187) published Figure 8.1 as a **chart only**; there is no underlying table, and the</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>- The closest modern source (US producer-price indices by industry, partitioned by Census concentration</t>
+          <t xml:space="preserve">  specific set of industries in Eichner's 1965-1973 "concentrated" and "competitive" aggregates is not</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ratios) uses incompatible industry classifications (1965-1973 SIC codes vs. post-1997 NAICS) and would</t>
+          <t xml:space="preserve">  recoverable from the published article.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t xml:space="preserve">  require re-selecting an industry set to mirror Eichner's — which is itself unrecoverable.</t>
+          <t>- The closest modern source (US producer-price indices by industry, partitioned by Census concentration</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>- Any modern continuation would therefore be a **proxy reconstruction**, not a faithful extension of the</t>
+          <t xml:space="preserve">  ratios) uses incompatible industry classifications (1965-1973 SIC codes vs. post-1997 NAICS) and would</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t xml:space="preserve">  original figure. Under the no-proxy and no-synthetic rules this is not undertaken; it would be a new</t>
+          <t xml:space="preserve">  require re-selecting an industry set to mirror Eichner's — which is itself unrecoverable.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t xml:space="preserve">  series requiring an explicit concept-match justification and human review.</t>
+          <t>- Any modern continuation would therefore be a **proxy reconstruction**, not a faithful extension of the</t>
         </is>
       </c>
     </row>
     <row r="123">
-      <c r="A123" t="inlineStr"/>
+      <c r="A123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  original figure. Under the no-proxy and no-synthetic rules this is not undertaken; it would be a new</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>## 3. Method</t>
+          <t xml:space="preserve">  series requiring an explicit concept-match justification and human review.</t>
         </is>
       </c>
     </row>
@@ -1947,24 +1951,24 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
+          <t>## 3. Method</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
           <t>The book-period values are a digitized reproduction (native-vector figure trace, overlay-validated). No</t>
         </is>
       </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>extension method is applied.</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>## 4. No-Proxy disclosure</t>
+          <t>extension method is applied.</t>
         </is>
       </c>
     </row>
@@ -1974,38 +1978,38 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>**No proxy used.** A modern producer-price reconstruction is *not* a proxy for Eichner's chart — it would be</t>
+          <t>## 4. No-Proxy disclosure</t>
         </is>
       </c>
     </row>
     <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>a re-construction requiring (a) a SIC-to-NAICS concordance, (b) re-application of concentration thresholds,</t>
-        </is>
-      </c>
+      <c r="A132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>and (c) selection of an industry set mirroring Eichner's (itself unrecoverable). Such a reconstruction would</t>
+          <t>**No proxy used.** A modern producer-price reconstruction is *not* a proxy for Eichner's chart — it would be</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>not meet the no-proxy bar without explicit human review.</t>
+          <t>a re-construction requiring (a) a SIC-to-NAICS concordance, (b) re-application of concentration thresholds,</t>
         </is>
       </c>
     </row>
     <row r="135">
-      <c r="A135" t="inlineStr"/>
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>and (c) selection of an industry set mirroring Eichner's (itself unrecoverable). Such a reconstruction would</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>## 5. No-Synthetic disclosure</t>
+          <t>not meet the no-proxy bar without explicit human review.</t>
         </is>
       </c>
     </row>
@@ -2015,24 +2019,24 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
+          <t>## 5. No-Synthetic disclosure</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
           <t>**None.** The book-period values are recovered by figure digitization (overlay-validated), not interpolated,</t>
         </is>
       </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>extrapolated, or synthetically generated. Digitization fidelity is flagged with `provenance: digitized`.</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>## 6. Failure-mode table</t>
+          <t>extrapolated, or synthetically generated. Digitization fidelity is flagged with `provenance: digitized`.</t>
         </is>
       </c>
     </row>
@@ -2042,45 +2046,45 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>| Failure | Action |</t>
+          <t>## 6. Failure-mode table</t>
         </is>
       </c>
     </row>
     <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>|---|---|</t>
-        </is>
-      </c>
+      <c r="A144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>| Loader cannot find recovered source workbook | Returns `{"status": "FAIL", "reason": "source_missing"}` |</t>
+          <t>| Failure | Action |</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>| Round-trip divergence against recovered workbook | FAIL — investigate the digitized workbook vs. the figure trace |</t>
+          <t>|---|---|</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>| Extension requested | Not applicable — a modern reconstruction would be a proxy (see §2) |</t>
+          <t>| Loader cannot find recovered source workbook | Returns `{"status": "FAIL", "reason": "source_missing"}` |</t>
         </is>
       </c>
     </row>
     <row r="148">
-      <c r="A148" t="inlineStr"/>
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>| Round-trip divergence against recovered workbook | FAIL — investigate the digitized workbook vs. the figure trace |</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>## 7. Predecessor divergence pre-disclosure</t>
+          <t>| Extension requested | Not applicable — a modern reconstruction would be a proxy (see §2) |</t>
         </is>
       </c>
     </row>
@@ -2090,31 +2094,31 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>No genuine predecessor per-series dataset matches this exhibit's content. The stub's earlier `S042` link was a</t>
+          <t>## 7. Predecessor divergence pre-disclosure</t>
         </is>
       </c>
     </row>
     <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>stale carryover from a Chapter 10 interest-rate series and has been nulled. A predecessor comparison is not</t>
-        </is>
-      </c>
+      <c r="A152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>meaningful here.</t>
+          <t>No genuine predecessor per-series dataset matches this exhibit's content. The stub's earlier `S042` link was a</t>
         </is>
       </c>
     </row>
     <row r="154">
-      <c r="A154" t="inlineStr"/>
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>stale carryover from a Chapter 10 interest-rate series and has been nulled. A predecessor comparison is not</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>## 8. Recovery record and future work</t>
+          <t>meaningful here.</t>
         </is>
       </c>
     </row>
@@ -2124,40 +2128,50 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>1. **Recovered (2026-05-26)**: native-vector trace of Shaikh's Figure 8.1 from the book PDF, overlay-validated,</t>
+          <t>## 8. Recovery record and future work</t>
         </is>
       </c>
     </row>
     <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   `provenance: digitized`. This is the current state of the series.</t>
-        </is>
-      </c>
+      <c r="A158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2. **Author's underlying spreadsheet** (out of scope): Alfred Eichner died in 1988; archived working papers may</t>
+          <t>1. **Recovered (2026-05-26)**: native-vector trace of Shaikh's Figure 8.1 from the book PDF, overlay-validated,</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t xml:space="preserve">   contain the original values, but these are not accessible to this project.</t>
+          <t xml:space="preserve">   `provenance: digitized`. This is the current state of the series.</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>3. **Modern producer-price reconstruction** (out of scope): would be a NEW series classified as a proxy</t>
+          <t>2. **Author's underlying spreadsheet** (out of scope): Alfred Eichner died in 1988; archived working papers may</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   contain the original values, but these are not accessible to this project.</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>3. **Modern producer-price reconstruction** (out of scope): would be a NEW series classified as a proxy</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
         <is>
           <t xml:space="preserve">   substitution, requiring a formal concept-match justification and human review — not an extension of S801.</t>
         </is>
@@ -2276,11 +2290,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2405,7 +2419,19 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-10T13:13:05.659471+00:00</t>
+          <t>2026-07-11T03:44:26.284749+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>label_variance_check</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>{"status": "PASS", "competitive_var": 154.529995, "oligopolistic_var": 81.136728, "rule": "var(Competitive) &gt; var(Oligopolistic) \u2014 concentrated line is smoother (Shaikh p.372)"}</t>
         </is>
       </c>
     </row>
@@ -2420,11 +2446,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2447,6 +2473,162 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>primary_source</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>EICHNER_1973_EJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>book_period_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>validation_class</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>pipeline_consistent</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>triage</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>{"verdict": "publish", "reason": "Faithful reconstruction of Shaikh Figure 8.1 (Ch8, p.372), which reproduces Eichner (1973, Economic Journal, p.1187): two wholesale-price-index lines (base 1957-59=100) for concentrated (oligopolistic) vs. competitive US industries, 1965-1973. Recovered 2026-05-26 from data_unavailable by offline vector extraction of Shaikh's figure, overlay-validated (n=18, MAE 0.0). Construction-relevant: opening exhibit of Shaikh's empirical critique of the administered-prices hypothesis. Single index axis; the two entities are an industry dimension, not separate units.", "date": "2026-06-11"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>dpr</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S801_DPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>epr</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S801_EPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>RSCD 2026-05-26: recovered by offline vector extraction of Shaikh Fig 8.1 from the book PDF (Oxford print p413, located in Robert's _PDF_LIBRARY), overlay-validated against the figure; flipped off data_unavailable (provenance: digitized). Two entities (Oligopolistic, Competitive), 1965-1973, index 1957-59=100; captures the late administered-price divergence (comp-&gt;145 vs olig-&gt;128.5 by 1973; the smoother/administered line is the OLIGOPOLISTIC one). F-T2-01 (2026-07-10): the two industry labels were TRANSPOSED at digitization and were corrected at the L01 loader (values unchanged; Competitive&lt;-&gt;Oligopolistic swapped). These are digitized price paths, not a recomputation (the concentrated/competitive industry membership is not separately recoverable). NB: CD2 S042 ('US Long-Run Interest Rates and Prices', a Ch10 Jastram series) is NOT a predecessor of S801 — known mismap (DPR section 8).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>content_type</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>cross_sectional</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>index_1957-59=100</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>proxy</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>publish</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>chapter</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
